--- a/Datos ESPARTACO/Parámetros para análisis de Antares/Resultados perfiles halpha 2018 y 2019 priorizando el sector naranja.xlsx
+++ b/Datos ESPARTACO/Parámetros para análisis de Antares/Resultados perfiles halpha 2018 y 2019 priorizando el sector naranja.xlsx
@@ -498,7 +498,7 @@
         <v>-0.000137</v>
       </c>
       <c r="F2" t="n">
-        <v>-40.9246</v>
+        <v>-40.9259</v>
       </c>
       <c r="G2" t="n">
         <v>0.1098</v>
@@ -533,7 +533,7 @@
         <v>1.1e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>3.4391</v>
+        <v>3.4392</v>
       </c>
       <c r="G3" t="n">
         <v>0.8004</v>
@@ -542,7 +542,7 @@
         <v>1.086</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9325</v>
+        <v>0.9326</v>
       </c>
     </row>
     <row r="4">
@@ -603,7 +603,7 @@
         <v>-0.00028</v>
       </c>
       <c r="F5" t="n">
-        <v>-83.96250000000001</v>
+        <v>-83.96850000000001</v>
       </c>
       <c r="G5" t="n">
         <v>0.07770000000000001</v>
@@ -702,22 +702,22 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>6562.008</v>
+        <v>6562.003</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.000122</v>
+        <v>-0.000123</v>
       </c>
       <c r="F8" t="n">
-        <v>-36.7212</v>
+        <v>-36.955</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1475</v>
+        <v>0.145</v>
       </c>
       <c r="H8" t="n">
-        <v>0.766</v>
+        <v>0.759</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1235</v>
+        <v>0.1185</v>
       </c>
     </row>
     <row r="9">
@@ -737,22 +737,22 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6562.948</v>
+        <v>6562.95</v>
       </c>
       <c r="E9" t="n">
         <v>2.1e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>6.2216</v>
+        <v>6.2895</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.8122</v>
       </c>
       <c r="H9" t="n">
-        <v>1.118</v>
+        <v>1.116</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9757</v>
+        <v>0.9689</v>
       </c>
     </row>
     <row r="10">
@@ -778,16 +778,16 @@
         <v>7.8e-05</v>
       </c>
       <c r="F10" t="n">
-        <v>23.4701</v>
+        <v>23.47</v>
       </c>
       <c r="G10" t="n">
         <v>0.5656</v>
       </c>
       <c r="H10" t="n">
-        <v>0.927</v>
+        <v>0.929</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5998</v>
+        <v>0.6011</v>
       </c>
     </row>
     <row r="11">
@@ -807,22 +807,22 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6562.272</v>
+        <v>6562.575</v>
       </c>
       <c r="E11" t="n">
-        <v>-8.2e-05</v>
+        <v>-3.6e-05</v>
       </c>
       <c r="F11" t="n">
-        <v>-24.6879</v>
+        <v>-10.8187</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1623</v>
+        <v>0.1629</v>
       </c>
       <c r="H11" t="n">
-        <v>1.383</v>
+        <v>1.911</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3288</v>
+        <v>0.416</v>
       </c>
     </row>
     <row r="12">
@@ -842,22 +842,22 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6562.96</v>
+        <v>6562.976</v>
       </c>
       <c r="E12" t="n">
-        <v>2.3e-05</v>
+        <v>2.5e-05</v>
       </c>
       <c r="F12" t="n">
-        <v>6.7643</v>
+        <v>7.4873</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9011</v>
+        <v>0.9569</v>
       </c>
       <c r="H12" t="n">
-        <v>1.104</v>
+        <v>1.091</v>
       </c>
       <c r="I12" t="n">
-        <v>1.0805</v>
+        <v>1.1354</v>
       </c>
     </row>
     <row r="13">
@@ -886,13 +886,13 @@
         <v>24.06</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5558</v>
+        <v>0.5551</v>
       </c>
       <c r="H13" t="n">
-        <v>0.865</v>
+        <v>0.89</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5472</v>
+        <v>0.5620000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -912,22 +912,22 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>6562.165</v>
+        <v>6562.022</v>
       </c>
       <c r="E14" t="n">
-        <v>-9.899999999999999e-05</v>
+        <v>-0.00012</v>
       </c>
       <c r="F14" t="n">
-        <v>-29.5569</v>
+        <v>-36.0982</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1769</v>
+        <v>0.0769</v>
       </c>
       <c r="H14" t="n">
-        <v>1.199</v>
+        <v>4.044</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3199</v>
+        <v>0.3732</v>
       </c>
     </row>
     <row r="15">
@@ -947,22 +947,22 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>6562.964</v>
+        <v>6563.01</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3e-05</v>
+        <v>3e-05</v>
       </c>
       <c r="F15" t="n">
-        <v>6.9449</v>
+        <v>9.0672</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8496</v>
+        <v>0.8492</v>
       </c>
       <c r="H15" t="n">
-        <v>1.124</v>
+        <v>1.051</v>
       </c>
       <c r="I15" t="n">
-        <v>1.0421</v>
+        <v>0.9826</v>
       </c>
     </row>
     <row r="16">
@@ -991,13 +991,13 @@
         <v>24.2</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5531</v>
+        <v>0.5483</v>
       </c>
       <c r="H16" t="n">
-        <v>0.887</v>
+        <v>0.913</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6073</v>
+        <v>0.6128</v>
       </c>
     </row>
     <row r="17">
@@ -1017,22 +1017,22 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>6562.147</v>
+        <v>6562.418</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.000101</v>
+        <v>-6e-05</v>
       </c>
       <c r="F17" t="n">
-        <v>-30.3781</v>
+        <v>-17.987</v>
       </c>
       <c r="G17" t="n">
-        <v>0.131</v>
+        <v>0.1249</v>
       </c>
       <c r="H17" t="n">
-        <v>1.254</v>
+        <v>2.001</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2463</v>
+        <v>0.3583</v>
       </c>
     </row>
     <row r="18">
@@ -1052,22 +1052,22 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>6563.011</v>
+        <v>6563.018</v>
       </c>
       <c r="E18" t="n">
-        <v>3e-05</v>
+        <v>3.1e-05</v>
       </c>
       <c r="F18" t="n">
-        <v>9.104200000000001</v>
+        <v>9.424099999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8531</v>
+        <v>0.8949</v>
       </c>
       <c r="H18" t="n">
-        <v>1.095</v>
+        <v>1.088</v>
       </c>
       <c r="I18" t="n">
-        <v>1.017</v>
+        <v>1.0641</v>
       </c>
     </row>
     <row r="19">
@@ -1096,13 +1096,13 @@
         <v>25.74</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5545</v>
+        <v>0.5524</v>
       </c>
       <c r="H19" t="n">
-        <v>0.831</v>
+        <v>0.848</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5351</v>
+        <v>0.5523</v>
       </c>
     </row>
     <row r="20">
@@ -1122,22 +1122,22 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>6561.989</v>
+        <v>6561.916</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.000125</v>
+        <v>-0.000136</v>
       </c>
       <c r="F20" t="n">
-        <v>-37.5859</v>
+        <v>-40.9153</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1229</v>
+        <v>0.1121</v>
       </c>
       <c r="H20" t="n">
-        <v>0.781</v>
+        <v>0.754</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1423</v>
+        <v>0.091</v>
       </c>
     </row>
     <row r="21">
@@ -1157,22 +1157,22 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>6563.049</v>
+        <v>6563.057</v>
       </c>
       <c r="E21" t="n">
-        <v>3.6e-05</v>
+        <v>3.7e-05</v>
       </c>
       <c r="F21" t="n">
-        <v>10.8285</v>
+        <v>11.1889</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7795</v>
+        <v>0.7705</v>
       </c>
       <c r="H21" t="n">
-        <v>1.056</v>
+        <v>1.039</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8879</v>
+        <v>0.8619</v>
       </c>
     </row>
     <row r="22">
@@ -1201,13 +1201,13 @@
         <v>26.07</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5597</v>
+        <v>0.5606</v>
       </c>
       <c r="H22" t="n">
         <v>0.896</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6183999999999999</v>
+        <v>0.6126</v>
       </c>
     </row>
     <row r="23">
@@ -1227,22 +1227,22 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>6562.161</v>
+        <v>6562.159</v>
       </c>
       <c r="E23" t="n">
         <v>-9.899999999999999e-05</v>
       </c>
       <c r="F23" t="n">
-        <v>-29.7496</v>
+        <v>-29.8086</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1628</v>
+        <v>0.1626</v>
       </c>
       <c r="H23" t="n">
-        <v>1.109</v>
+        <v>1.106</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2716</v>
+        <v>0.271</v>
       </c>
     </row>
     <row r="24">
@@ -1262,22 +1262,22 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>6563.026</v>
+        <v>6563.027</v>
       </c>
       <c r="E24" t="n">
         <v>3.3e-05</v>
       </c>
       <c r="F24" t="n">
-        <v>9.797599999999999</v>
+        <v>9.8093</v>
       </c>
       <c r="G24" t="n">
-        <v>0.8391999999999999</v>
+        <v>0.8389</v>
       </c>
       <c r="H24" t="n">
-        <v>1.094</v>
+        <v>1.093</v>
       </c>
       <c r="I24" t="n">
-        <v>0.9891</v>
+        <v>0.9883999999999999</v>
       </c>
     </row>
     <row r="25">
@@ -1332,22 +1332,22 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>6562.144</v>
+        <v>6562.146</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.000102</v>
+        <v>-0.000101</v>
       </c>
       <c r="F26" t="n">
-        <v>-30.5055</v>
+        <v>-30.4259</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1257</v>
+        <v>0.1266</v>
       </c>
       <c r="H26" t="n">
-        <v>0.926</v>
+        <v>0.93</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1764</v>
+        <v>0.1785</v>
       </c>
     </row>
     <row r="27">
@@ -1367,22 +1367,22 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>6563.023</v>
+        <v>6563.024</v>
       </c>
       <c r="E27" t="n">
         <v>3.2e-05</v>
       </c>
       <c r="F27" t="n">
-        <v>9.653499999999999</v>
+        <v>9.6805</v>
       </c>
       <c r="G27" t="n">
-        <v>0.8202</v>
+        <v>0.8195</v>
       </c>
       <c r="H27" t="n">
-        <v>1.107</v>
+        <v>1.109</v>
       </c>
       <c r="I27" t="n">
-        <v>0.978</v>
+        <v>0.9785</v>
       </c>
     </row>
     <row r="28">
@@ -1411,13 +1411,13 @@
         <v>26.66</v>
       </c>
       <c r="G28" t="n">
-        <v>0.5604</v>
+        <v>0.5605</v>
       </c>
       <c r="H28" t="n">
-        <v>0.969</v>
+        <v>0.967</v>
       </c>
       <c r="I28" t="n">
-        <v>0.6516999999999999</v>
+        <v>0.6563</v>
       </c>
     </row>
     <row r="29">
@@ -1437,22 +1437,22 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>6561.987</v>
+        <v>6562.143</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.000126</v>
+        <v>-0.000102</v>
       </c>
       <c r="F29" t="n">
-        <v>-37.6957</v>
+        <v>-30.5629</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2705</v>
+        <v>0.4792</v>
       </c>
       <c r="H29" t="n">
-        <v>0.823</v>
+        <v>1.07</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2388</v>
+        <v>0.8097</v>
       </c>
     </row>
     <row r="30">
@@ -1472,22 +1472,22 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>6562.884</v>
+        <v>6562.816</v>
       </c>
       <c r="E30" t="n">
-        <v>1.1e-05</v>
+        <v>1e-06</v>
       </c>
       <c r="F30" t="n">
-        <v>3.2709</v>
+        <v>0.1636</v>
       </c>
       <c r="G30" t="n">
-        <v>0.8961</v>
+        <v>1.0344</v>
       </c>
       <c r="H30" t="n">
-        <v>1.168</v>
+        <v>1.26</v>
       </c>
       <c r="I30" t="n">
-        <v>1.1347</v>
+        <v>1.478</v>
       </c>
     </row>
     <row r="31">
@@ -1516,13 +1516,13 @@
         <v>22.5</v>
       </c>
       <c r="G31" t="n">
-        <v>0.5625</v>
+        <v>0.5322</v>
       </c>
       <c r="H31" t="n">
-        <v>1.011</v>
+        <v>0.961</v>
       </c>
       <c r="I31" t="n">
-        <v>0.6853</v>
+        <v>0.6093</v>
       </c>
     </row>
   </sheetData>

--- a/Datos ESPARTACO/Parámetros para análisis de Antares/Resultados perfiles halpha 2018 y 2019 priorizando el sector naranja.xlsx
+++ b/Datos ESPARTACO/Parámetros para análisis de Antares/Resultados perfiles halpha 2018 y 2019 priorizando el sector naranja.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,20 +456,25 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Velocidad [km/s]</t>
+          <t>Velocidad obs. [km/s]</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Velocidad heliocéntrica [km/s]</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Profundidad / Altura</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>FWHM [Å]</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>EW [Å]</t>
         </is>
@@ -492,22 +497,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>6561.916</v>
+        <v>6561.874</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.000137</v>
+        <v>-0.000143</v>
       </c>
       <c r="F2" t="n">
-        <v>-40.9259</v>
+        <v>-42.83</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1098</v>
+        <v>-65.66</v>
       </c>
       <c r="H2" t="n">
-        <v>0.696</v>
+        <v>0.1032</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0819</v>
+        <v>0.678</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.0751</v>
       </c>
     </row>
     <row r="3">
@@ -527,22 +535,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6562.887</v>
+        <v>6562.893</v>
       </c>
       <c r="E3" t="n">
-        <v>1.1e-05</v>
+        <v>1.2e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>3.4392</v>
+        <v>3.68</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8004</v>
+        <v>-19.15</v>
       </c>
       <c r="H3" t="n">
-        <v>1.086</v>
+        <v>0.8008</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9326</v>
+        <v>1.076</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.924</v>
       </c>
     </row>
     <row r="4">
@@ -571,13 +582,16 @@
         <v>19.71</v>
       </c>
       <c r="G4" t="n">
+        <v>-3.12</v>
+      </c>
+      <c r="H4" t="n">
         <v>0.5629</v>
       </c>
-      <c r="H4" t="n">
-        <v>0.9429999999999999</v>
-      </c>
       <c r="I4" t="n">
-        <v>0.6163</v>
+        <v>0.9419999999999999</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.6153999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -597,22 +611,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6560.974</v>
+        <v>6561.847</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.00028</v>
+        <v>-0.000147</v>
       </c>
       <c r="F5" t="n">
-        <v>-83.96850000000001</v>
+        <v>-44.1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.07770000000000001</v>
+        <v>-67.97</v>
       </c>
       <c r="H5" t="n">
-        <v>4.044</v>
+        <v>0.1367</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3686</v>
+        <v>0.947</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.1734</v>
       </c>
     </row>
     <row r="6">
@@ -632,22 +649,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6562.914</v>
+        <v>6562.896</v>
       </c>
       <c r="E6" t="n">
-        <v>1.5e-05</v>
+        <v>1.3e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>4.6448</v>
+        <v>3.82</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8252</v>
+        <v>-20.05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.012</v>
+        <v>0.7941</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9162</v>
+        <v>1.066</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.9095</v>
       </c>
     </row>
     <row r="7">
@@ -676,13 +696,16 @@
         <v>19.4</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5504</v>
+        <v>-4.47</v>
       </c>
       <c r="H7" t="n">
-        <v>0.959</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6089</v>
+        <v>0.963</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.6576</v>
       </c>
     </row>
     <row r="8">
@@ -702,22 +725,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>6562.003</v>
+        <v>6561.974</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.000123</v>
+        <v>-0.000128</v>
       </c>
       <c r="F8" t="n">
-        <v>-36.955</v>
+        <v>-38.27</v>
       </c>
       <c r="G8" t="n">
-        <v>0.145</v>
+        <v>-64.27</v>
       </c>
       <c r="H8" t="n">
-        <v>0.759</v>
+        <v>0.1374</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1185</v>
+        <v>0.738</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.1083</v>
       </c>
     </row>
     <row r="9">
@@ -737,22 +763,25 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6562.95</v>
+        <v>6562.956</v>
       </c>
       <c r="E9" t="n">
-        <v>2.1e-05</v>
+        <v>2.2e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>6.2895</v>
+        <v>6.57</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8122</v>
+        <v>-19.43</v>
       </c>
       <c r="H9" t="n">
-        <v>1.116</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9689</v>
+        <v>1.105</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.9581</v>
       </c>
     </row>
     <row r="10">
@@ -781,13 +810,16 @@
         <v>23.47</v>
       </c>
       <c r="G10" t="n">
+        <v>-2.53</v>
+      </c>
+      <c r="H10" t="n">
         <v>0.5656</v>
       </c>
-      <c r="H10" t="n">
-        <v>0.929</v>
-      </c>
       <c r="I10" t="n">
-        <v>0.6011</v>
+        <v>0.928</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.6006</v>
       </c>
     </row>
     <row r="11">
@@ -807,22 +839,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6562.575</v>
+        <v>6561.932</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.6e-05</v>
+        <v>-0.000134</v>
       </c>
       <c r="F11" t="n">
-        <v>-10.8187</v>
+        <v>-40.21</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1629</v>
+        <v>-66.8</v>
       </c>
       <c r="H11" t="n">
-        <v>1.911</v>
+        <v>0.1167</v>
       </c>
       <c r="I11" t="n">
-        <v>0.416</v>
+        <v>0.775</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.1086</v>
       </c>
     </row>
     <row r="12">
@@ -842,22 +877,25 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6562.976</v>
+        <v>6562.994</v>
       </c>
       <c r="E12" t="n">
-        <v>2.5e-05</v>
+        <v>2.8e-05</v>
       </c>
       <c r="F12" t="n">
-        <v>7.4873</v>
+        <v>8.33</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9569</v>
+        <v>-18.26</v>
       </c>
       <c r="H12" t="n">
-        <v>1.091</v>
+        <v>0.8317</v>
       </c>
       <c r="I12" t="n">
-        <v>1.1354</v>
+        <v>1.056</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.9479</v>
       </c>
     </row>
     <row r="13">
@@ -886,13 +924,16 @@
         <v>24.06</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5551</v>
+        <v>-2.53</v>
       </c>
       <c r="H13" t="n">
-        <v>0.89</v>
+        <v>0.5595</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.846</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.536</v>
       </c>
     </row>
     <row r="14">
@@ -912,22 +953,25 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>6562.022</v>
+        <v>6561.971</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.00012</v>
+        <v>-0.000128</v>
       </c>
       <c r="F14" t="n">
-        <v>-36.0982</v>
+        <v>-38.4</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0769</v>
+        <v>-65.98</v>
       </c>
       <c r="H14" t="n">
-        <v>4.044</v>
+        <v>0.1378</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3732</v>
+        <v>0.895</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.1697</v>
       </c>
     </row>
     <row r="15">
@@ -947,22 +991,25 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>6563.01</v>
+        <v>6562.991</v>
       </c>
       <c r="E15" t="n">
-        <v>3e-05</v>
+        <v>2.7e-05</v>
       </c>
       <c r="F15" t="n">
-        <v>9.0672</v>
+        <v>8.18</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8492</v>
+        <v>-19.4</v>
       </c>
       <c r="H15" t="n">
-        <v>1.051</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9826</v>
+        <v>1.082</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.951</v>
       </c>
     </row>
     <row r="16">
@@ -991,13 +1038,16 @@
         <v>24.2</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5483</v>
+        <v>-3.38</v>
       </c>
       <c r="H16" t="n">
-        <v>0.913</v>
+        <v>0.5556</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6128</v>
+        <v>0.873</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.5994</v>
       </c>
     </row>
     <row r="17">
@@ -1017,22 +1067,25 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>6562.418</v>
+        <v>6561.948</v>
       </c>
       <c r="E17" t="n">
-        <v>-6e-05</v>
+        <v>-0.000132</v>
       </c>
       <c r="F17" t="n">
-        <v>-17.987</v>
+        <v>-39.49</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1249</v>
+        <v>-67.68000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>2.001</v>
+        <v>0.1122</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3583</v>
+        <v>0.878</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.1357</v>
       </c>
     </row>
     <row r="18">
@@ -1052,22 +1105,25 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>6563.018</v>
+        <v>6563.03</v>
       </c>
       <c r="E18" t="n">
-        <v>3.1e-05</v>
+        <v>3.3e-05</v>
       </c>
       <c r="F18" t="n">
-        <v>9.424099999999999</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8949</v>
+        <v>-18.24</v>
       </c>
       <c r="H18" t="n">
-        <v>1.088</v>
+        <v>0.8247</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0641</v>
+        <v>1.064</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.9523</v>
       </c>
     </row>
     <row r="19">
@@ -1096,13 +1152,16 @@
         <v>25.74</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5524</v>
+        <v>-2.45</v>
       </c>
       <c r="H19" t="n">
-        <v>0.848</v>
+        <v>0.5563</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5523</v>
+        <v>0.824</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.5276</v>
       </c>
     </row>
     <row r="20">
@@ -1122,22 +1181,25 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>6561.916</v>
+        <v>6561.917</v>
       </c>
       <c r="E20" t="n">
         <v>-0.000136</v>
       </c>
       <c r="F20" t="n">
-        <v>-40.9153</v>
+        <v>-40.9</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1121</v>
+        <v>-70.11</v>
       </c>
       <c r="H20" t="n">
+        <v>0.1122</v>
+      </c>
+      <c r="I20" t="n">
         <v>0.754</v>
       </c>
-      <c r="I20" t="n">
-        <v>0.091</v>
+      <c r="J20" t="n">
+        <v>0.0912</v>
       </c>
     </row>
     <row r="21">
@@ -1163,16 +1225,19 @@
         <v>3.7e-05</v>
       </c>
       <c r="F21" t="n">
-        <v>11.1889</v>
+        <v>11.19</v>
       </c>
       <c r="G21" t="n">
+        <v>-18.02</v>
+      </c>
+      <c r="H21" t="n">
         <v>0.7705</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>1.039</v>
       </c>
-      <c r="I21" t="n">
-        <v>0.8619</v>
+      <c r="J21" t="n">
+        <v>0.862</v>
       </c>
     </row>
     <row r="22">
@@ -1201,12 +1266,15 @@
         <v>26.07</v>
       </c>
       <c r="G22" t="n">
+        <v>-3.14</v>
+      </c>
+      <c r="H22" t="n">
         <v>0.5606</v>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>0.896</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>0.6126</v>
       </c>
     </row>
@@ -1227,22 +1295,25 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>6562.159</v>
+        <v>6562.001</v>
       </c>
       <c r="E23" t="n">
-        <v>-9.899999999999999e-05</v>
+        <v>-0.000124</v>
       </c>
       <c r="F23" t="n">
-        <v>-29.8086</v>
+        <v>-37.03</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1626</v>
+        <v>-66.5</v>
       </c>
       <c r="H23" t="n">
-        <v>1.106</v>
+        <v>0.1343</v>
       </c>
       <c r="I23" t="n">
-        <v>0.271</v>
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.1702</v>
       </c>
     </row>
     <row r="24">
@@ -1262,22 +1333,25 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>6563.027</v>
+        <v>6563.047</v>
       </c>
       <c r="E24" t="n">
-        <v>3.3e-05</v>
+        <v>3.6e-05</v>
       </c>
       <c r="F24" t="n">
-        <v>9.8093</v>
+        <v>10.74</v>
       </c>
       <c r="G24" t="n">
-        <v>0.8389</v>
+        <v>-18.73</v>
       </c>
       <c r="H24" t="n">
-        <v>1.093</v>
+        <v>0.8136</v>
       </c>
       <c r="I24" t="n">
-        <v>0.9883999999999999</v>
+        <v>1.06</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.9274</v>
       </c>
     </row>
     <row r="25">
@@ -1306,13 +1380,16 @@
         <v>26.94</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5601</v>
+        <v>-2.53</v>
       </c>
       <c r="H25" t="n">
-        <v>0.875</v>
+        <v>0.5613</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6022999999999999</v>
+        <v>0.862</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.5947</v>
       </c>
     </row>
     <row r="26">
@@ -1332,22 +1409,25 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>6562.146</v>
+        <v>6561.975</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.000101</v>
+        <v>-0.000128</v>
       </c>
       <c r="F26" t="n">
-        <v>-30.4259</v>
+        <v>-38.23</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1266</v>
+        <v>-67.59</v>
       </c>
       <c r="H26" t="n">
-        <v>0.93</v>
+        <v>0.0979</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1785</v>
+        <v>0.841</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.0886</v>
       </c>
     </row>
     <row r="27">
@@ -1367,22 +1447,25 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>6563.024</v>
+        <v>6563.041</v>
       </c>
       <c r="E27" t="n">
-        <v>3.2e-05</v>
+        <v>3.5e-05</v>
       </c>
       <c r="F27" t="n">
-        <v>9.6805</v>
+        <v>10.45</v>
       </c>
       <c r="G27" t="n">
-        <v>0.8195</v>
+        <v>-18.91</v>
       </c>
       <c r="H27" t="n">
-        <v>1.109</v>
+        <v>0.7994</v>
       </c>
       <c r="I27" t="n">
-        <v>0.9785</v>
+        <v>1.076</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.9251</v>
       </c>
     </row>
     <row r="28">
@@ -1411,13 +1494,16 @@
         <v>26.66</v>
       </c>
       <c r="G28" t="n">
-        <v>0.5605</v>
+        <v>-2.7</v>
       </c>
       <c r="H28" t="n">
-        <v>0.967</v>
+        <v>0.5615</v>
       </c>
       <c r="I28" t="n">
-        <v>0.6563</v>
+        <v>0.961</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.6451</v>
       </c>
     </row>
     <row r="29">
@@ -1437,22 +1523,25 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>6562.143</v>
+        <v>6562.021</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.000102</v>
+        <v>-0.00012</v>
       </c>
       <c r="F29" t="n">
-        <v>-30.5629</v>
+        <v>-36.12</v>
       </c>
       <c r="G29" t="n">
-        <v>0.4792</v>
+        <v>-62.36</v>
       </c>
       <c r="H29" t="n">
-        <v>1.07</v>
+        <v>0.3388</v>
       </c>
       <c r="I29" t="n">
-        <v>0.8097</v>
+        <v>0.961</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.4558</v>
       </c>
     </row>
     <row r="30">
@@ -1472,22 +1561,25 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>6562.816</v>
+        <v>6562.867</v>
       </c>
       <c r="E30" t="n">
-        <v>1e-06</v>
+        <v>8e-06</v>
       </c>
       <c r="F30" t="n">
-        <v>0.1636</v>
+        <v>2.51</v>
       </c>
       <c r="G30" t="n">
-        <v>1.0344</v>
+        <v>-23.73</v>
       </c>
       <c r="H30" t="n">
-        <v>1.26</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>1.478</v>
+        <v>1.186</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.2452</v>
       </c>
     </row>
     <row r="31">
@@ -1516,13 +1608,16 @@
         <v>22.5</v>
       </c>
       <c r="G31" t="n">
-        <v>0.5322</v>
+        <v>-3.74</v>
       </c>
       <c r="H31" t="n">
-        <v>0.961</v>
+        <v>0.5371</v>
       </c>
       <c r="I31" t="n">
-        <v>0.6093</v>
+        <v>0.9419999999999999</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.5981</v>
       </c>
     </row>
   </sheetData>

--- a/Datos ESPARTACO/Parámetros para análisis de Antares/Resultados perfiles halpha 2018 y 2019 priorizando el sector naranja.xlsx
+++ b/Datos ESPARTACO/Parámetros para análisis de Antares/Resultados perfiles halpha 2018 y 2019 priorizando el sector naranja.xlsx
@@ -499,8 +499,10 @@
       <c r="D2" t="n">
         <v>6561.874</v>
       </c>
-      <c r="E2" t="n">
-        <v>-0.000143</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>-0.00014</t>
+        </is>
       </c>
       <c r="F2" t="n">
         <v>-42.83</v>
@@ -509,13 +511,13 @@
         <v>-65.66</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1032</v>
+        <v>0.1</v>
       </c>
       <c r="I2" t="n">
-        <v>0.678</v>
+        <v>0.68</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0751</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="3">
@@ -537,8 +539,10 @@
       <c r="D3" t="n">
         <v>6562.893</v>
       </c>
-      <c r="E3" t="n">
-        <v>1.2e-05</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1.2e-05</t>
+        </is>
       </c>
       <c r="F3" t="n">
         <v>3.68</v>
@@ -547,13 +551,13 @@
         <v>-19.15</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8008</v>
+        <v>0.8</v>
       </c>
       <c r="I3" t="n">
-        <v>1.076</v>
+        <v>1.08</v>
       </c>
       <c r="J3" t="n">
-        <v>0.924</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="4">
@@ -575,8 +579,10 @@
       <c r="D4" t="n">
         <v>6563.829</v>
       </c>
-      <c r="E4" t="n">
-        <v>6.600000000000001e-05</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>6.6e-05</t>
+        </is>
       </c>
       <c r="F4" t="n">
         <v>19.71</v>
@@ -585,13 +591,13 @@
         <v>-3.12</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5629</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6153999999999999</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="5">
@@ -613,8 +619,10 @@
       <c r="D5" t="n">
         <v>6561.847</v>
       </c>
-      <c r="E5" t="n">
-        <v>-0.000147</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>-0.00015</t>
+        </is>
       </c>
       <c r="F5" t="n">
         <v>-44.1</v>
@@ -623,13 +631,13 @@
         <v>-67.97</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1367</v>
+        <v>0.14</v>
       </c>
       <c r="I5" t="n">
-        <v>0.947</v>
+        <v>0.95</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1734</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="6">
@@ -651,8 +659,10 @@
       <c r="D6" t="n">
         <v>6562.896</v>
       </c>
-      <c r="E6" t="n">
-        <v>1.3e-05</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1.3e-05</t>
+        </is>
       </c>
       <c r="F6" t="n">
         <v>3.82</v>
@@ -661,13 +671,13 @@
         <v>-20.05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7941</v>
+        <v>0.79</v>
       </c>
       <c r="I6" t="n">
-        <v>1.066</v>
+        <v>1.07</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9095</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="7">
@@ -689,8 +699,10 @@
       <c r="D7" t="n">
         <v>6563.822</v>
       </c>
-      <c r="E7" t="n">
-        <v>6.499999999999999e-05</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>6.5e-05</t>
+        </is>
       </c>
       <c r="F7" t="n">
         <v>19.4</v>
@@ -699,13 +711,13 @@
         <v>-4.47</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>0.963</v>
+        <v>0.96</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6576</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="8">
@@ -727,8 +739,10 @@
       <c r="D8" t="n">
         <v>6561.974</v>
       </c>
-      <c r="E8" t="n">
-        <v>-0.000128</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>-0.00013</t>
+        </is>
       </c>
       <c r="F8" t="n">
         <v>-38.27</v>
@@ -737,13 +751,13 @@
         <v>-64.27</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1374</v>
+        <v>0.14</v>
       </c>
       <c r="I8" t="n">
-        <v>0.738</v>
+        <v>0.74</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1083</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="9">
@@ -765,8 +779,10 @@
       <c r="D9" t="n">
         <v>6562.956</v>
       </c>
-      <c r="E9" t="n">
-        <v>2.2e-05</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2.2e-05</t>
+        </is>
       </c>
       <c r="F9" t="n">
         <v>6.57</v>
@@ -775,13 +791,13 @@
         <v>-19.43</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>1.105</v>
+        <v>1.11</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9581</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="10">
@@ -803,8 +819,10 @@
       <c r="D10" t="n">
         <v>6563.911</v>
       </c>
-      <c r="E10" t="n">
-        <v>7.8e-05</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>7.8e-05</t>
+        </is>
       </c>
       <c r="F10" t="n">
         <v>23.47</v>
@@ -813,13 +831,13 @@
         <v>-2.53</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5656</v>
+        <v>0.57</v>
       </c>
       <c r="I10" t="n">
-        <v>0.928</v>
+        <v>0.93</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6006</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="11">
@@ -841,8 +859,10 @@
       <c r="D11" t="n">
         <v>6561.932</v>
       </c>
-      <c r="E11" t="n">
-        <v>-0.000134</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>-0.00013</t>
+        </is>
       </c>
       <c r="F11" t="n">
         <v>-40.21</v>
@@ -851,13 +871,13 @@
         <v>-66.8</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1167</v>
+        <v>0.12</v>
       </c>
       <c r="I11" t="n">
-        <v>0.775</v>
+        <v>0.77</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1086</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="12">
@@ -879,8 +899,10 @@
       <c r="D12" t="n">
         <v>6562.994</v>
       </c>
-      <c r="E12" t="n">
-        <v>2.8e-05</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2.8e-05</t>
+        </is>
       </c>
       <c r="F12" t="n">
         <v>8.33</v>
@@ -889,13 +911,13 @@
         <v>-18.26</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8317</v>
+        <v>0.83</v>
       </c>
       <c r="I12" t="n">
-        <v>1.056</v>
+        <v>1.06</v>
       </c>
       <c r="J12" t="n">
-        <v>0.9479</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="13">
@@ -917,8 +939,10 @@
       <c r="D13" t="n">
         <v>6563.924</v>
       </c>
-      <c r="E13" t="n">
-        <v>8.000000000000001e-05</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>8e-05</t>
+        </is>
       </c>
       <c r="F13" t="n">
         <v>24.06</v>
@@ -927,13 +951,13 @@
         <v>-2.53</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5595</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>0.846</v>
+        <v>0.85</v>
       </c>
       <c r="J13" t="n">
-        <v>0.536</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="14">
@@ -955,8 +979,10 @@
       <c r="D14" t="n">
         <v>6561.971</v>
       </c>
-      <c r="E14" t="n">
-        <v>-0.000128</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>-0.00013</t>
+        </is>
       </c>
       <c r="F14" t="n">
         <v>-38.4</v>
@@ -965,13 +991,13 @@
         <v>-65.98</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1378</v>
+        <v>0.14</v>
       </c>
       <c r="I14" t="n">
-        <v>0.895</v>
+        <v>0.89</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1697</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="15">
@@ -993,8 +1019,10 @@
       <c r="D15" t="n">
         <v>6562.991</v>
       </c>
-      <c r="E15" t="n">
-        <v>2.7e-05</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2.7e-05</t>
+        </is>
       </c>
       <c r="F15" t="n">
         <v>8.18</v>
@@ -1003,13 +1031,13 @@
         <v>-19.4</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>1.082</v>
+        <v>1.08</v>
       </c>
       <c r="J15" t="n">
-        <v>0.951</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="16">
@@ -1031,8 +1059,10 @@
       <c r="D16" t="n">
         <v>6563.927</v>
       </c>
-      <c r="E16" t="n">
-        <v>8.1e-05</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>8.1e-05</t>
+        </is>
       </c>
       <c r="F16" t="n">
         <v>24.2</v>
@@ -1041,13 +1071,13 @@
         <v>-3.38</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5556</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>0.873</v>
+        <v>0.87</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5994</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="17">
@@ -1069,8 +1099,10 @@
       <c r="D17" t="n">
         <v>6561.948</v>
       </c>
-      <c r="E17" t="n">
-        <v>-0.000132</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>-0.00013</t>
+        </is>
       </c>
       <c r="F17" t="n">
         <v>-39.49</v>
@@ -1079,13 +1111,13 @@
         <v>-67.68000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1122</v>
+        <v>0.11</v>
       </c>
       <c r="I17" t="n">
-        <v>0.878</v>
+        <v>0.88</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1357</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="18">
@@ -1107,8 +1139,10 @@
       <c r="D18" t="n">
         <v>6563.03</v>
       </c>
-      <c r="E18" t="n">
-        <v>3.3e-05</v>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>3.3e-05</t>
+        </is>
       </c>
       <c r="F18" t="n">
         <v>9.949999999999999</v>
@@ -1117,13 +1151,13 @@
         <v>-18.24</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8247</v>
+        <v>0.82</v>
       </c>
       <c r="I18" t="n">
-        <v>1.064</v>
+        <v>1.06</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9523</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="19">
@@ -1145,8 +1179,10 @@
       <c r="D19" t="n">
         <v>6563.961</v>
       </c>
-      <c r="E19" t="n">
-        <v>8.6e-05</v>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>8.6e-05</t>
+        </is>
       </c>
       <c r="F19" t="n">
         <v>25.74</v>
@@ -1155,13 +1191,13 @@
         <v>-2.45</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5563</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>0.824</v>
+        <v>0.82</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5276</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="20">
@@ -1183,8 +1219,10 @@
       <c r="D20" t="n">
         <v>6561.917</v>
       </c>
-      <c r="E20" t="n">
-        <v>-0.000136</v>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>-0.00014</t>
+        </is>
       </c>
       <c r="F20" t="n">
         <v>-40.9</v>
@@ -1193,13 +1231,13 @@
         <v>-70.11</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1122</v>
+        <v>0.11</v>
       </c>
       <c r="I20" t="n">
-        <v>0.754</v>
+        <v>0.75</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0912</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="21">
@@ -1221,8 +1259,10 @@
       <c r="D21" t="n">
         <v>6563.057</v>
       </c>
-      <c r="E21" t="n">
-        <v>3.7e-05</v>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>3.7e-05</t>
+        </is>
       </c>
       <c r="F21" t="n">
         <v>11.19</v>
@@ -1231,13 +1271,13 @@
         <v>-18.02</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7705</v>
+        <v>0.77</v>
       </c>
       <c r="I21" t="n">
-        <v>1.039</v>
+        <v>1.04</v>
       </c>
       <c r="J21" t="n">
-        <v>0.862</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="22">
@@ -1259,8 +1299,10 @@
       <c r="D22" t="n">
         <v>6563.968</v>
       </c>
-      <c r="E22" t="n">
-        <v>8.7e-05</v>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>8.7e-05</t>
+        </is>
       </c>
       <c r="F22" t="n">
         <v>26.07</v>
@@ -1269,13 +1311,13 @@
         <v>-3.14</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5606</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>0.896</v>
+        <v>0.9</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6126</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="23">
@@ -1297,8 +1339,10 @@
       <c r="D23" t="n">
         <v>6562.001</v>
       </c>
-      <c r="E23" t="n">
-        <v>-0.000124</v>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>-0.00012</t>
+        </is>
       </c>
       <c r="F23" t="n">
         <v>-37.03</v>
@@ -1307,13 +1351,13 @@
         <v>-66.5</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1343</v>
+        <v>0.13</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1702</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="24">
@@ -1335,8 +1379,10 @@
       <c r="D24" t="n">
         <v>6563.047</v>
       </c>
-      <c r="E24" t="n">
-        <v>3.6e-05</v>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>3.6e-05</t>
+        </is>
       </c>
       <c r="F24" t="n">
         <v>10.74</v>
@@ -1345,13 +1391,13 @@
         <v>-18.73</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8136</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I24" t="n">
         <v>1.06</v>
       </c>
       <c r="J24" t="n">
-        <v>0.9274</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="25">
@@ -1373,8 +1419,10 @@
       <c r="D25" t="n">
         <v>6563.987</v>
       </c>
-      <c r="E25" t="n">
-        <v>9.000000000000001e-05</v>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>9e-05</t>
+        </is>
       </c>
       <c r="F25" t="n">
         <v>26.94</v>
@@ -1383,13 +1431,13 @@
         <v>-2.53</v>
       </c>
       <c r="H25" t="n">
-        <v>0.5613</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>0.862</v>
+        <v>0.86</v>
       </c>
       <c r="J25" t="n">
-        <v>0.5947</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="26">
@@ -1411,8 +1459,10 @@
       <c r="D26" t="n">
         <v>6561.975</v>
       </c>
-      <c r="E26" t="n">
-        <v>-0.000128</v>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>-0.00013</t>
+        </is>
       </c>
       <c r="F26" t="n">
         <v>-38.23</v>
@@ -1421,13 +1471,13 @@
         <v>-67.59</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0979</v>
+        <v>0.1</v>
       </c>
       <c r="I26" t="n">
-        <v>0.841</v>
+        <v>0.84</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0886</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="27">
@@ -1449,8 +1499,10 @@
       <c r="D27" t="n">
         <v>6563.041</v>
       </c>
-      <c r="E27" t="n">
-        <v>3.5e-05</v>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>3.5e-05</t>
+        </is>
       </c>
       <c r="F27" t="n">
         <v>10.45</v>
@@ -1459,13 +1511,13 @@
         <v>-18.91</v>
       </c>
       <c r="H27" t="n">
-        <v>0.7994</v>
+        <v>0.8</v>
       </c>
       <c r="I27" t="n">
-        <v>1.076</v>
+        <v>1.08</v>
       </c>
       <c r="J27" t="n">
-        <v>0.9251</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="28">
@@ -1487,8 +1539,10 @@
       <c r="D28" t="n">
         <v>6563.981</v>
       </c>
-      <c r="E28" t="n">
-        <v>8.899999999999999e-05</v>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>8.9e-05</t>
+        </is>
       </c>
       <c r="F28" t="n">
         <v>26.66</v>
@@ -1497,13 +1551,13 @@
         <v>-2.7</v>
       </c>
       <c r="H28" t="n">
-        <v>0.5615</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>0.961</v>
+        <v>0.96</v>
       </c>
       <c r="J28" t="n">
-        <v>0.6451</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="29">
@@ -1525,8 +1579,10 @@
       <c r="D29" t="n">
         <v>6562.021</v>
       </c>
-      <c r="E29" t="n">
-        <v>-0.00012</v>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>-0.00012</t>
+        </is>
       </c>
       <c r="F29" t="n">
         <v>-36.12</v>
@@ -1535,13 +1591,13 @@
         <v>-62.36</v>
       </c>
       <c r="H29" t="n">
-        <v>0.3388</v>
+        <v>0.34</v>
       </c>
       <c r="I29" t="n">
-        <v>0.961</v>
+        <v>0.96</v>
       </c>
       <c r="J29" t="n">
-        <v>0.4558</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="30">
@@ -1563,8 +1619,10 @@
       <c r="D30" t="n">
         <v>6562.867</v>
       </c>
-      <c r="E30" t="n">
-        <v>8e-06</v>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>8.4e-06</t>
+        </is>
       </c>
       <c r="F30" t="n">
         <v>2.51</v>
@@ -1573,13 +1631,13 @@
         <v>-23.73</v>
       </c>
       <c r="H30" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.93</v>
       </c>
       <c r="I30" t="n">
-        <v>1.186</v>
+        <v>1.19</v>
       </c>
       <c r="J30" t="n">
-        <v>1.2452</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="31">
@@ -1601,8 +1659,10 @@
       <c r="D31" t="n">
         <v>6563.89</v>
       </c>
-      <c r="E31" t="n">
-        <v>7.499999999999999e-05</v>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>7.5e-05</t>
+        </is>
       </c>
       <c r="F31" t="n">
         <v>22.5</v>
@@ -1611,13 +1671,13 @@
         <v>-3.74</v>
       </c>
       <c r="H31" t="n">
-        <v>0.5371</v>
+        <v>0.54</v>
       </c>
       <c r="I31" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="J31" t="n">
-        <v>0.5981</v>
+        <v>0.6</v>
       </c>
     </row>
   </sheetData>

--- a/Datos ESPARTACO/Parámetros para análisis de Antares/Resultados perfiles halpha 2018 y 2019 priorizando el sector naranja.xlsx
+++ b/Datos ESPARTACO/Parámetros para análisis de Antares/Resultados perfiles halpha 2018 y 2019 priorizando el sector naranja.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1563,7 +1563,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Agosto 05-2019</t>
+          <t>Septiembre 21-2018</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1577,33 +1577,33 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>6562.021</v>
+        <v>6561.865</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>-0.00012</t>
+          <t>-0.00014</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>-36.12</v>
+        <v>-43.24</v>
       </c>
       <c r="G29" t="n">
-        <v>-62.36</v>
+        <v>-71.54000000000001</v>
       </c>
       <c r="H29" t="n">
-        <v>0.34</v>
+        <v>0.1</v>
       </c>
       <c r="I29" t="n">
-        <v>0.96</v>
+        <v>1.3</v>
       </c>
       <c r="J29" t="n">
-        <v>0.46</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Agosto 05-2019</t>
+          <t>Septiembre 21-2018</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1617,67 +1617,307 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>6562.867</v>
+        <v>6562.984</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>8.4e-06</t>
+          <t>2.6e-05</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.51</v>
+        <v>7.85</v>
       </c>
       <c r="G30" t="n">
-        <v>-23.73</v>
+        <v>-20.45</v>
       </c>
       <c r="H30" t="n">
-        <v>0.93</v>
+        <v>0.76</v>
       </c>
       <c r="I30" t="n">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="J30" t="n">
-        <v>1.25</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>Septiembre 21-2018</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Hα</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Absorción Cobalto</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>6563.927</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>8.1e-05</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>24.23</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-4.07</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>Agosto 05-2019</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Hα</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Emisión Azul Hα</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>6562.02</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>-0.00012</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>-36.19</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-62.43</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Agosto 05-2019</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Hα</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Absorción Hα</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>6562.895</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>1.3e-05</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-22.45</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Agosto 05-2019</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Hα</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
         <is>
           <t>Absorción Cobalto</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="D34" t="n">
         <v>6563.89</v>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>7.5e-05</t>
         </is>
       </c>
-      <c r="F31" t="n">
+      <c r="F34" t="n">
         <v>22.5</v>
       </c>
-      <c r="G31" t="n">
+      <c r="G34" t="n">
         <v>-3.74</v>
       </c>
-      <c r="H31" t="n">
+      <c r="H34" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Agosto 06-2019</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Hα</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Emisión Azul Hα</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>6562.015</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>-0.00012</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>-36.39</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-62.82</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Agosto 06-2019</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Hα</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Absorción Hα</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>6562.907</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>1.5e-05</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-22.08</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Agosto 06-2019</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Hα</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Absorción Cobalto</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>6563.907</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>7.8e-05</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-3.13</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="J37" t="n">
         <v>0.54</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0.6</v>
       </c>
     </row>
   </sheetData>
